--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,7 +1413,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>218547</v>
+        <v>218925</v>
       </c>
       <c r="B8" t="n">
         <v>103356</v>
@@ -1446,20 +1446,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Byrum "Bränslevägen", Öl</t>
+          <t>Byrum SO, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619455.2115196231</v>
+        <v>619428.9849502131</v>
       </c>
       <c r="R8" t="n">
-        <v>6344017.555867328</v>
+        <v>6344042.253245787</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,7 +1497,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2007-07-10</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1493,7 +1507,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2007-07-10</t>
+          <t>2010-06-06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1509,26 +1523,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vägkant i tallskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Thomas Gunnarsson, Ingrid Johnsson, Lennart Johnsson, Ulla-Britt Andersson, Jan-Olof Petersson, Peter Ståhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>218925</v>
+        <v>2279128</v>
       </c>
       <c r="B9" t="n">
-        <v>103356</v>
+        <v>96224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,40 +1556,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>671</v>
+        <v>219769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1579,10 +1589,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619428.9849502131</v>
+        <v>619443.7840291818</v>
       </c>
       <c r="R9" t="n">
-        <v>6344042.253245787</v>
+        <v>6344037.266210712</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1656,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2279128</v>
+        <v>219394</v>
       </c>
       <c r="B10" t="n">
-        <v>96224</v>
+        <v>103356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1668,43 +1678,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219769</v>
+        <v>671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Byrum SO, Öl</t>
+          <t>700 m SO Bränsle, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619443.7840291818</v>
+        <v>619480.0079017935</v>
       </c>
       <c r="R10" t="n">
-        <v>6344037.266210712</v>
+        <v>6344004.734031709</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1731,7 +1745,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1741,7 +1755,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2010-06-06</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1760,28 +1774,23 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>vägkant i tallskog</t>
+          <t>Skogskörväg i gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ingrid Johnsson, Lennart Johnsson, Ulla-Britt Andersson, Jan-Olof Petersson, Peter Ståhl</t>
+          <t>Göran Wendt, Vera Wendt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>219394</v>
+        <v>87371</v>
       </c>
       <c r="B11" t="n">
-        <v>103356</v>
+        <v>97511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1790,47 +1799,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>671</v>
+        <v>174</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>700 m SO Bränsle, Öl</t>
+          <t>800 m SO Bränsle, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619480.0079017935</v>
+        <v>619438.0388480658</v>
       </c>
       <c r="R11" t="n">
-        <v>6344004.734031709</v>
+        <v>6344029.515827562</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1857,7 +1866,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1867,7 +1876,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1886,20 +1895,25 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Skogskörväg i gran</t>
+          <t>Tallbryn, 3 m SV vägen</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Göran Wendt</t>
+        </is>
+      </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Wendt, Vera Wendt</t>
+          <t>Göran Wendt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87371</v>
+        <v>87370</v>
       </c>
       <c r="B12" t="n">
         <v>97511</v>
@@ -1934,7 +1948,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1948,10 +1962,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619438.0388480658</v>
+        <v>619475.3316136569</v>
       </c>
       <c r="R12" t="n">
-        <v>6344029.515827562</v>
+        <v>6343997.556272103</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2007,7 +2021,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallbryn, 3 m SV vägen</t>
+          <t>Norra vägrenen</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2025,10 +2039,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>87370</v>
+        <v>219418</v>
       </c>
       <c r="B13" t="n">
-        <v>97511</v>
+        <v>103356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2037,35 +2051,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>174</v>
+        <v>671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2074,10 +2088,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619475.3316136569</v>
+        <v>619438.0388480658</v>
       </c>
       <c r="R13" t="n">
-        <v>6343997.556272103</v>
+        <v>6344029.515827562</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2122,6 +2136,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>400 ex spridda längs 100 m</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2133,7 +2152,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Norra vägrenen</t>
+          <t>Södra vägdiket</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2151,10 +2170,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>219418</v>
+        <v>2279737</v>
       </c>
       <c r="B14" t="n">
-        <v>103356</v>
+        <v>96224</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2163,47 +2182,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>671</v>
+        <v>219769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>800 m SO Bränsle, Öl</t>
+          <t>700 m SO Bränsle, Öl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619438.0388480658</v>
+        <v>619480.0079017935</v>
       </c>
       <c r="R14" t="n">
-        <v>6344029.515827562</v>
+        <v>6344004.734031709</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2230,7 +2240,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2240,7 +2250,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2248,11 +2258,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>400 ex spridda längs 100 m</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2264,28 +2269,23 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Södra vägdiket</t>
+          <t>Skogskörväg i gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Göran Wendt</t>
-        </is>
-      </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Wendt</t>
+          <t>Göran Wendt, Vera Wendt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2279737</v>
+        <v>67088883</v>
       </c>
       <c r="B15" t="n">
-        <v>96224</v>
+        <v>103357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2294,38 +2294,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219769</v>
+        <v>671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>700 m SO Bränsle, Öl</t>
+          <t>Bränsle 500 m SO, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619480.0079017935</v>
+        <v>619427.6331913753</v>
       </c>
       <c r="R15" t="n">
-        <v>6344004.734031709</v>
+        <v>6344051.422540787</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2352,7 +2355,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2017-08-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2362,7 +2365,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2010-07-08</t>
+          <t>2017-08-09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2379,22 +2382,22 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Skogskörväg i gran</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Wendt, Vera Wendt</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>67088883</v>
+        <v>6892894</v>
       </c>
       <c r="B16" t="n">
         <v>103357</v>
@@ -2433,14 +2436,14 @@
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bränsle 500 m SO, Öl</t>
+          <t>Bränsle, 500 m SO, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619427.6331913753</v>
+        <v>619389.2409993303</v>
       </c>
       <c r="R16" t="n">
-        <v>6344051.422540787</v>
+        <v>6344083.891810247</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2467,7 +2470,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-08-09</t>
+          <t>2013-08-06</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2477,7 +2480,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-08-09</t>
+          <t>2013-08-06</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2493,72 +2496,74 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Crister Albinsson, Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6892894</v>
+        <v>2914449</v>
       </c>
       <c r="B17" t="n">
-        <v>103357</v>
+        <v>96312</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bränsle, 500 m SO, Öl</t>
+          <t>Byrum "Bränslevägen", Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619389.2409993303</v>
+        <v>619455.2115196231</v>
       </c>
       <c r="R17" t="n">
-        <v>6344083.891810247</v>
+        <v>6344017.555867328</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2582,7 +2587,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2013-08-06</t>
+          <t>2007-07-10</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2592,7 +2597,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2013-08-06</t>
+          <t>2007-07-10</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2608,28 +2613,23 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gles tallskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Crister Albinsson, Jan-Olof Petersson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2914449</v>
+        <v>2913834</v>
       </c>
       <c r="B18" t="n">
         <v>96312</v>
@@ -2662,17 +2662,26 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Byrum "Bränslevägen", Öl</t>
+          <t>Byrum söder, Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619455.2115196231</v>
+        <v>619452.759387641</v>
       </c>
       <c r="R18" t="n">
-        <v>6344017.555867328</v>
+        <v>6344027.234935808</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2699,7 +2708,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2007-07-10</t>
+          <t>2007-06-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2709,7 +2718,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2007-07-10</t>
+          <t>2007-06-25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2725,23 +2734,28 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2913834</v>
+        <v>2921244</v>
       </c>
       <c r="B19" t="n">
         <v>96312</v>
@@ -2774,11 +2788,7 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>blomknopp</t>
@@ -2786,14 +2796,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Byrum söder, Öl</t>
+          <t>Bränsle 500m SO, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619452.759387641</v>
+        <v>619428.9063689227</v>
       </c>
       <c r="R19" t="n">
-        <v>6344027.234935808</v>
+        <v>6344044.959362451</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2820,7 +2830,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2007-06-25</t>
+          <t>2009-06-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2830,7 +2840,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2007-06-25</t>
+          <t>2009-06-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2849,7 +2859,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2860,65 +2870,76 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Jan-Olof Petersson, Crister Albinsson, Stina Eriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2921244</v>
+        <v>103312351</v>
       </c>
       <c r="B20" t="n">
-        <v>96312</v>
+        <v>103357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bränsle 500m SO, Öl</t>
+          <t>Bränsle 500 m SO, Öl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619428.9063689227</v>
+        <v>619483.340303674</v>
       </c>
       <c r="R20" t="n">
-        <v>6344044.959362451</v>
+        <v>6344002.122413431</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2942,7 +2963,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2009-06-23</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2952,7 +2973,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2009-06-23</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2966,82 +2987,66 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson, Crister Albinsson, Stina Eriksson</t>
+          <t>Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103312351</v>
+        <v>87295376</v>
       </c>
       <c r="B21" t="n">
-        <v>103357</v>
+        <v>96312</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bränsle 500 m SO, Öl</t>
+          <t>Bränslevägen, Öl</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3051,7 +3056,7 @@
         <v>6344002.122413431</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3075,7 +3080,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3085,7 +3090,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3103,25 +3108,30 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>skogsstig genom blandskog</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>87295376</v>
+        <v>87295382</v>
       </c>
       <c r="B22" t="n">
-        <v>96312</v>
+        <v>96225</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3134,26 +3144,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3240,10 +3254,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>87295382</v>
+        <v>95764169</v>
       </c>
       <c r="B23" t="n">
-        <v>96225</v>
+        <v>103226</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3252,46 +3266,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219769</v>
+        <v>340</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bränslevägen, Öl</t>
+          <t>Bränsle SO, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619483.340303674</v>
+        <v>619465.2086582868</v>
       </c>
       <c r="R23" t="n">
-        <v>6344002.122413431</v>
+        <v>6344009.720982418</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3316,9 +3334,14 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Hö-Bor-8992</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2006-08-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3328,7 +3351,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2006-08-10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3346,30 +3369,29 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>skogsstig genom blandskog</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Vera Wendt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95764169</v>
+        <v>101607741</v>
       </c>
       <c r="B24" t="n">
-        <v>103226</v>
+        <v>103357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3378,50 +3400,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>340</v>
+        <v>671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bränsle SO, Öl</t>
+          <t>Byrum S om, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619465.2086582868</v>
+        <v>619475.5517258242</v>
       </c>
       <c r="R24" t="n">
-        <v>6344009.720982418</v>
+        <v>6343989.979052952</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3446,14 +3460,9 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Hö-Bor-8992</t>
-        </is>
-      </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2006-08-10</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3463,7 +3472,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2006-08-10</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3484,261 +3493,15 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Carl-Axel Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vera Wendt</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>101607741</v>
-      </c>
-      <c r="B25" t="n">
-        <v>103357</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>671</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Gotlandsmåra</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Galium rotundifolium</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Byrum S om, Öl</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>619475.5517258242</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6343989.979052952</v>
-      </c>
-      <c r="S25" t="n">
-        <v>25</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Böda</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
           <t>Carl-Axel Andersson</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Carl-Axel Andersson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>111951526</v>
-      </c>
-      <c r="B26" t="n">
-        <v>103742</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>340</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Bränsle SO, Öl</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>619465</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6344010</v>
-      </c>
-      <c r="S26" t="n">
-        <v>25</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Borgholm</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Öland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Böda</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Hö-Bor-8992</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lokalen såg ganska ok ut men nära vägen fanns stora bestånd av örnbräken som konkurrerar.</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -3508,7 +3508,7 @@
         <v>126806892</v>
       </c>
       <c r="B25" t="n">
-        <v>99578</v>
+        <v>99653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -3508,7 +3508,7 @@
         <v>126806892</v>
       </c>
       <c r="B25" t="n">
-        <v>99653</v>
+        <v>99659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -3508,7 +3508,7 @@
         <v>126806892</v>
       </c>
       <c r="B25" t="n">
-        <v>99659</v>
+        <v>99660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -3508,7 +3508,7 @@
         <v>126806892</v>
       </c>
       <c r="B25" t="n">
-        <v>99660</v>
+        <v>99664</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,12 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>103356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619428.9063689227</v>
+        <v>619429</v>
       </c>
       <c r="R7" t="n">
-        <v>6344044.959362451</v>
+        <v>6344045</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1365,19 +1360,9 @@
           <t>2009-06-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2009-06-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,7 +1392,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
@@ -2282,15 +2267,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67088883</v>
+        <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>103357</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105703</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2315,20 +2295,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bränsle 500 m SO, Öl</t>
+          <t>Bränsle, 700 m SO, Öl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>619427.6331913753</v>
+        <v>619477</v>
       </c>
       <c r="R15" t="n">
-        <v>6344051.422540787</v>
+        <v>6344012</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2353,24 +2342,19 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Hö-Bor-4202</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,25 +2363,35 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Skogskörväg i gran</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Göran Wendt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6892894</v>
+        <v>67088883</v>
       </c>
       <c r="B16" t="n">
         <v>103357</v>
@@ -2436,14 +2430,14 @@
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bränsle, 500 m SO, Öl</t>
+          <t>Bränsle 500 m SO, Öl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619389.2409993303</v>
+        <v>619427.6331913753</v>
       </c>
       <c r="R16" t="n">
-        <v>6344083.891810247</v>
+        <v>6344051.422540787</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2470,7 +2464,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2013-08-06</t>
+          <t>2017-08-09</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2480,7 +2474,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2013-08-06</t>
+          <t>2017-08-09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2496,74 +2490,72 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gles tallskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Crister Albinsson, Jan-Olof Petersson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2914449</v>
+        <v>6892894</v>
       </c>
       <c r="B17" t="n">
-        <v>96312</v>
+        <v>103357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Byrum "Bränslevägen", Öl</t>
+          <t>Bränsle, 500 m SO, Öl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>619455.2115196231</v>
+        <v>619389.2409993303</v>
       </c>
       <c r="R17" t="n">
-        <v>6344017.555867328</v>
+        <v>6344083.891810247</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2587,7 +2579,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2007-07-10</t>
+          <t>2013-08-06</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2597,7 +2589,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2007-07-10</t>
+          <t>2013-08-06</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2613,23 +2605,28 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gles tallskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Crister Albinsson, Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2913834</v>
+        <v>2914449</v>
       </c>
       <c r="B18" t="n">
         <v>96312</v>
@@ -2662,26 +2659,17 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Byrum söder, Öl</t>
+          <t>Byrum "Bränslevägen", Öl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619452.759387641</v>
+        <v>619455.2115196231</v>
       </c>
       <c r="R18" t="n">
-        <v>6344027.234935808</v>
+        <v>6344017.555867328</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2708,7 +2696,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2007-06-25</t>
+          <t>2007-07-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2718,7 +2706,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2007-06-25</t>
+          <t>2007-07-10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2734,28 +2722,23 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2921244</v>
+        <v>2913834</v>
       </c>
       <c r="B19" t="n">
         <v>96312</v>
@@ -2788,7 +2771,11 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>blomknopp</t>
@@ -2796,14 +2783,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bränsle 500m SO, Öl</t>
+          <t>Byrum söder, Öl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619428.9063689227</v>
+        <v>619452.759387641</v>
       </c>
       <c r="R19" t="n">
-        <v>6344044.959362451</v>
+        <v>6344027.234935808</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2830,7 +2817,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2009-06-23</t>
+          <t>2007-06-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2840,7 +2827,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2009-06-23</t>
+          <t>2007-06-25</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2859,7 +2846,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2870,76 +2857,65 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson, Crister Albinsson, Stina Eriksson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103312351</v>
+        <v>2921244</v>
       </c>
       <c r="B20" t="n">
-        <v>103357</v>
+        <v>96312</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>671</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bränsle 500 m SO, Öl</t>
+          <t>Bränsle 500m SO, Öl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619483.340303674</v>
+        <v>619428.9063689227</v>
       </c>
       <c r="R20" t="n">
-        <v>6344002.122413431</v>
+        <v>6344044.959362451</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2963,7 +2939,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2009-06-23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2973,7 +2949,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2009-06-23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2987,66 +2963,82 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Jan-Olof Petersson, Crister Albinsson, Stina Eriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>87295376</v>
+        <v>103312351</v>
       </c>
       <c r="B21" t="n">
-        <v>96312</v>
+        <v>103357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bränslevägen, Öl</t>
+          <t>Bränsle 500 m SO, Öl</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3056,7 +3048,7 @@
         <v>6344002.122413431</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3080,7 +3072,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3090,7 +3082,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3108,30 +3100,25 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>skogsstig genom blandskog</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Stefan Kasselstrand, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>87295382</v>
+        <v>87295376</v>
       </c>
       <c r="B22" t="n">
-        <v>96225</v>
+        <v>96312</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3144,30 +3131,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219769</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3254,10 +3237,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95764169</v>
+        <v>87295382</v>
       </c>
       <c r="B23" t="n">
-        <v>103226</v>
+        <v>96225</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3266,50 +3249,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>340</v>
+        <v>219769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bränsle SO, Öl</t>
+          <t>Bränslevägen, Öl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619465.2086582868</v>
+        <v>619483.340303674</v>
       </c>
       <c r="R23" t="n">
-        <v>6344009.720982418</v>
+        <v>6344002.122413431</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3334,14 +3313,9 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Hö-Bor-8992</t>
-        </is>
-      </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2006-08-10</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3351,7 +3325,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2006-08-10</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3369,73 +3343,77 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>skogsstig genom blandskog</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vera Wendt</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101607741</v>
+        <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>103357</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>671</v>
+        <v>340</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gotlandsmåra</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Galium rotundifolium</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Byrum S om, Öl</t>
+          <t>Bränsle SO, Öl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619475.5517258242</v>
+        <v>619465</v>
       </c>
       <c r="R24" t="n">
-        <v>6343989.979052952</v>
+        <v>6344010</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3460,24 +3438,19 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Hö-Bor-8992</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3493,73 +3466,70 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Vera Wendt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126806892</v>
+        <v>101607741</v>
       </c>
       <c r="B25" t="n">
-        <v>99664</v>
+        <v>103357</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>174</v>
+        <v>671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bränslevägen, Böda, Öl</t>
+          <t>Byrum S om, Öl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>619483</v>
+        <v>619475.5517258242</v>
       </c>
       <c r="R25" t="n">
-        <v>6344002</v>
+        <v>6343989.979052952</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3586,12 +3556,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3607,15 +3587,129 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Carl-Axel Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Carl-Axel Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126806892</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99664</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>174</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Strävlosta</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bromopsis benekenii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bränslevägen, Böda, Öl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>619483</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6344002</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Lennart Sundh</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Lennart Sundh</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>105703</v>
+        <v>105715</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>105703</v>
+        <v>105715</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>105570</v>
+        <v>105582</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>105715</v>
+        <v>105724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>105715</v>
+        <v>105724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>105582</v>
+        <v>105591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>105724</v>
+        <v>105736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>105724</v>
+        <v>105736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>105591</v>
+        <v>105603</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>105736</v>
+        <v>105745</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>105736</v>
+        <v>105745</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>105603</v>
+        <v>105612</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>105745</v>
+        <v>105750</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>105745</v>
+        <v>105750</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>105612</v>
+        <v>105615</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>105750</v>
+        <v>105778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>105750</v>
+        <v>105778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>105615</v>
+        <v>105643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>105778</v>
+        <v>105784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>105778</v>
+        <v>105784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>105643</v>
+        <v>105649</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 57656-2020 artfynd.xlsx
+++ b/artfynd/A 57656-2020 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>218918</v>
       </c>
       <c r="B7" t="n">
-        <v>105805</v>
+        <v>105810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>219396</v>
       </c>
       <c r="B15" t="n">
-        <v>105805</v>
+        <v>105810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>95764169</v>
       </c>
       <c r="B24" t="n">
-        <v>105670</v>
+        <v>105675</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
